--- a/docs/heros.xlsx
+++ b/docs/heros.xlsx
@@ -34,16 +34,16 @@
     <t>CRT %</t>
   </si>
   <si>
-    <t>PHV %</t>
-  </si>
-  <si>
-    <t>MAV %</t>
+    <t>VPH %</t>
+  </si>
+  <si>
+    <t>VMA %</t>
   </si>
   <si>
     <t>EVA %</t>
   </si>
   <si>
-    <t>RPV %</t>
+    <t>REC%</t>
   </si>
   <si>
     <t>REL</t>
@@ -380,7 +380,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -392,13 +392,18 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,8 +422,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="14"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -430,6 +441,28 @@
       <left style="thin">
         <color indexed="10"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="10"/>
       </right>
@@ -443,7 +476,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
         <color indexed="11"/>
@@ -452,7 +485,7 @@
         <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -461,43 +494,28 @@
         <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
         <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,28 +524,58 @@
         <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
@@ -537,38 +585,44 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,8 +642,10 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
       <rgbColor rgb="ffdbdbdb"/>
     </indexedColors>
@@ -608,10 +664,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -788,11 +844,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -801,33 +860,33 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
-          <a:lnSpc>
-            <a:spcPct val="100000"/>
-          </a:lnSpc>
-          <a:spcBef>
-            <a:spcPts val="0"/>
-          </a:spcBef>
-          <a:spcAft>
-            <a:spcPts val="0"/>
-          </a:spcAft>
-          <a:buClrTx/>
-          <a:buSzTx/>
-          <a:buFontTx/>
-          <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1066,12 +1125,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1352,7 +1411,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1620,29 +1679,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:T12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.7656" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.71094" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7266" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.75781" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.4062" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.71094" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.07812" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.24219" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.72656" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.07812" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.72656" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6406" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.53125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.90625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.2266" style="1" customWidth="1"/>
-    <col min="19" max="19" width="18.8984" style="1" customWidth="1"/>
-    <col min="20" max="20" width="59.3125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8516" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.67188" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6719" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85156" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.67188" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.17188" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.35156" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.67188" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85156" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.17188" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.67188" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.17188" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6719" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.85156" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1719" style="1" customWidth="1"/>
+    <col min="19" max="19" width="18.8516" style="1" customWidth="1"/>
+    <col min="20" max="20" width="59.3516" style="1" customWidth="1"/>
     <col min="21" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1650,703 +1709,703 @@
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" t="s" s="4">
+      <c r="A2" s="5"/>
+      <c r="B2" t="s" s="6">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="4">
+      <c r="C2" t="s" s="6">
         <v>2</v>
       </c>
-      <c r="D2" t="s" s="4">
+      <c r="D2" t="s" s="6">
         <v>3</v>
       </c>
-      <c r="E2" t="s" s="4">
+      <c r="E2" t="s" s="6">
         <v>4</v>
       </c>
-      <c r="F2" t="s" s="4">
+      <c r="F2" t="s" s="6">
         <v>5</v>
       </c>
-      <c r="G2" t="s" s="4">
+      <c r="G2" t="s" s="6">
         <v>6</v>
       </c>
-      <c r="H2" t="s" s="4">
+      <c r="H2" t="s" s="6">
         <v>7</v>
       </c>
-      <c r="I2" t="s" s="4">
+      <c r="I2" t="s" s="6">
         <v>8</v>
       </c>
-      <c r="J2" t="s" s="4">
+      <c r="J2" t="s" s="6">
         <v>9</v>
       </c>
-      <c r="K2" t="s" s="4">
+      <c r="K2" t="s" s="6">
         <v>10</v>
       </c>
-      <c r="L2" t="s" s="4">
+      <c r="L2" t="s" s="6">
         <v>11</v>
       </c>
-      <c r="M2" t="s" s="4">
+      <c r="M2" t="s" s="6">
         <v>12</v>
       </c>
-      <c r="N2" t="s" s="4">
+      <c r="N2" t="s" s="6">
         <v>13</v>
       </c>
-      <c r="O2" t="s" s="4">
+      <c r="O2" t="s" s="6">
         <v>14</v>
       </c>
-      <c r="P2" t="s" s="4">
+      <c r="P2" t="s" s="6">
         <v>15</v>
       </c>
-      <c r="Q2" t="s" s="4">
+      <c r="Q2" t="s" s="6">
         <v>16</v>
       </c>
-      <c r="R2" t="s" s="4">
+      <c r="R2" t="s" s="6">
         <v>17</v>
       </c>
-      <c r="S2" t="s" s="4">
+      <c r="S2" t="s" s="6">
         <v>18</v>
       </c>
-      <c r="T2" t="s" s="4">
+      <c r="T2" t="s" s="6">
         <v>19</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
-      <c r="A3" t="s" s="5">
+      <c r="A3" t="s" s="7">
         <v>20</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="B3" t="s" s="8">
         <v>21</v>
       </c>
-      <c r="C3" t="s" s="7">
+      <c r="C3" t="s" s="9">
         <v>22</v>
       </c>
-      <c r="D3" t="s" s="7">
+      <c r="D3" t="s" s="9">
         <v>23</v>
       </c>
-      <c r="E3" t="s" s="7">
+      <c r="E3" t="s" s="9">
         <v>24</v>
       </c>
-      <c r="F3" t="s" s="7">
+      <c r="F3" t="s" s="9">
         <v>25</v>
       </c>
-      <c r="G3" t="s" s="7">
+      <c r="G3" t="s" s="9">
         <v>26</v>
       </c>
-      <c r="H3" t="s" s="7">
+      <c r="H3" t="s" s="9">
         <v>27</v>
       </c>
-      <c r="I3" t="s" s="7">
+      <c r="I3" t="s" s="9">
         <v>28</v>
       </c>
-      <c r="J3" t="s" s="7">
+      <c r="J3" t="s" s="9">
         <v>29</v>
       </c>
-      <c r="K3" t="s" s="7">
+      <c r="K3" t="s" s="9">
         <v>30</v>
       </c>
-      <c r="L3" t="s" s="7">
+      <c r="L3" t="s" s="9">
         <v>31</v>
       </c>
-      <c r="M3" t="s" s="7">
+      <c r="M3" t="s" s="9">
         <v>32</v>
       </c>
-      <c r="N3" t="s" s="7">
+      <c r="N3" t="s" s="9">
         <v>33</v>
       </c>
-      <c r="O3" t="s" s="7">
-        <v>34</v>
-      </c>
-      <c r="P3" t="s" s="7">
+      <c r="O3" t="s" s="9">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s" s="9">
         <v>35</v>
       </c>
-      <c r="Q3" t="s" s="7">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s" s="7">
-        <v>34</v>
-      </c>
-      <c r="S3" t="s" s="7">
+      <c r="Q3" t="s" s="9">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s" s="9">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="T3" t="s" s="7">
+      <c r="T3" t="s" s="9">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="32.05" customHeight="1">
-      <c r="A4" t="s" s="8">
+      <c r="A4" t="s" s="10">
         <v>38</v>
       </c>
-      <c r="B4" t="s" s="9">
+      <c r="B4" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="C4" t="s" s="10">
+      <c r="C4" t="s" s="12">
         <v>22</v>
       </c>
-      <c r="D4" t="s" s="10">
+      <c r="D4" t="s" s="12">
         <v>39</v>
       </c>
-      <c r="E4" t="s" s="10">
+      <c r="E4" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="F4" t="s" s="10">
+      <c r="F4" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="G4" t="s" s="10">
+      <c r="G4" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="H4" t="s" s="10">
+      <c r="H4" t="s" s="12">
         <v>43</v>
       </c>
-      <c r="I4" t="s" s="10">
+      <c r="I4" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="J4" t="s" s="10">
+      <c r="J4" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K4" t="s" s="10">
+      <c r="K4" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L4" t="s" s="10">
+      <c r="L4" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="M4" t="s" s="10">
+      <c r="M4" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="N4" t="s" s="10">
+      <c r="N4" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="O4" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="P4" t="s" s="10">
+      <c r="O4" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="Q4" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="R4" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="S4" t="s" s="10">
+      <c r="Q4" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="S4" t="s" s="12">
         <v>47</v>
       </c>
-      <c r="T4" t="s" s="10">
+      <c r="T4" t="s" s="12">
         <v>48</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" t="s" s="8">
+      <c r="A5" t="s" s="10">
         <v>49</v>
       </c>
-      <c r="B5" t="s" s="9">
+      <c r="B5" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="C5" t="s" s="10">
+      <c r="C5" t="s" s="12">
         <v>22</v>
       </c>
-      <c r="D5" t="s" s="10">
+      <c r="D5" t="s" s="12">
         <v>50</v>
       </c>
-      <c r="E5" t="s" s="10">
+      <c r="E5" t="s" s="12">
         <v>51</v>
       </c>
-      <c r="F5" t="s" s="10">
+      <c r="F5" t="s" s="12">
         <v>52</v>
       </c>
-      <c r="G5" t="s" s="10">
+      <c r="G5" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="H5" t="s" s="10">
+      <c r="H5" t="s" s="12">
         <v>54</v>
       </c>
-      <c r="I5" t="s" s="10">
+      <c r="I5" t="s" s="12">
         <v>55</v>
       </c>
-      <c r="J5" t="s" s="10">
+      <c r="J5" t="s" s="12">
         <v>56</v>
       </c>
-      <c r="K5" t="s" s="10">
+      <c r="K5" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L5" t="s" s="10">
+      <c r="L5" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="M5" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="N5" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="P5" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="Q5" t="s" s="10">
+      <c r="M5" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="O5" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="P5" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="R5" t="s" s="10">
+      <c r="R5" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="S5" t="s" s="10">
+      <c r="S5" t="s" s="12">
         <v>57</v>
       </c>
-      <c r="T5" t="s" s="10">
+      <c r="T5" t="s" s="12">
         <v>58</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" t="s" s="8">
+      <c r="A6" t="s" s="10">
         <v>59</v>
       </c>
-      <c r="B6" t="s" s="9">
+      <c r="B6" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="C6" t="s" s="10">
+      <c r="C6" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="D6" t="s" s="10">
+      <c r="D6" t="s" s="12">
         <v>61</v>
       </c>
-      <c r="E6" t="s" s="10">
+      <c r="E6" t="s" s="12">
         <v>62</v>
       </c>
-      <c r="F6" t="s" s="10">
+      <c r="F6" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="G6" t="s" s="10">
+      <c r="G6" t="s" s="12">
         <v>63</v>
       </c>
-      <c r="H6" t="s" s="10">
+      <c r="H6" t="s" s="12">
         <v>64</v>
       </c>
-      <c r="I6" t="s" s="10">
+      <c r="I6" t="s" s="12">
         <v>65</v>
       </c>
-      <c r="J6" t="s" s="10">
+      <c r="J6" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K6" t="s" s="10">
+      <c r="K6" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L6" t="s" s="10">
+      <c r="L6" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M6" t="s" s="10">
+      <c r="M6" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="N6" t="s" s="10">
+      <c r="N6" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="O6" t="s" s="10">
+      <c r="O6" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="P6" t="s" s="10">
+      <c r="P6" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="Q6" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s" s="10">
+      <c r="Q6" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="R6" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="S6" t="s" s="10">
+      <c r="S6" t="s" s="12">
         <v>68</v>
       </c>
-      <c r="T6" t="s" s="10">
+      <c r="T6" t="s" s="12">
         <v>69</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" t="s" s="8">
+      <c r="A7" t="s" s="10">
         <v>70</v>
       </c>
-      <c r="B7" t="s" s="9">
+      <c r="B7" t="s" s="11">
         <v>71</v>
       </c>
-      <c r="C7" t="s" s="10">
+      <c r="C7" t="s" s="12">
         <v>22</v>
       </c>
-      <c r="D7" t="s" s="10">
+      <c r="D7" t="s" s="12">
         <v>72</v>
       </c>
-      <c r="E7" t="s" s="10">
+      <c r="E7" t="s" s="12">
         <v>73</v>
       </c>
-      <c r="F7" t="s" s="10">
+      <c r="F7" t="s" s="12">
         <v>74</v>
       </c>
-      <c r="G7" t="s" s="10">
+      <c r="G7" t="s" s="12">
         <v>75</v>
       </c>
-      <c r="H7" t="s" s="10">
+      <c r="H7" t="s" s="12">
         <v>76</v>
       </c>
-      <c r="I7" t="s" s="10">
+      <c r="I7" t="s" s="12">
         <v>77</v>
       </c>
-      <c r="J7" t="s" s="10">
+      <c r="J7" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K7" t="s" s="10">
+      <c r="K7" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L7" t="s" s="10">
+      <c r="L7" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M7" t="s" s="10">
+      <c r="M7" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="N7" t="s" s="10">
+      <c r="N7" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="O7" t="s" s="10">
+      <c r="O7" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="P7" t="s" s="10">
+      <c r="P7" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="Q7" t="s" s="10">
+      <c r="Q7" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="R7" t="s" s="10">
+      <c r="R7" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="S7" t="s" s="10">
+      <c r="S7" t="s" s="12">
         <v>78</v>
       </c>
-      <c r="T7" t="s" s="10">
+      <c r="T7" t="s" s="12">
         <v>79</v>
       </c>
     </row>
     <row r="8" ht="32.05" customHeight="1">
-      <c r="A8" t="s" s="8">
+      <c r="A8" t="s" s="10">
         <v>80</v>
       </c>
-      <c r="B8" t="s" s="9">
+      <c r="B8" t="s" s="11">
         <v>71</v>
       </c>
-      <c r="C8" t="s" s="10">
+      <c r="C8" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="D8" t="s" s="10">
+      <c r="D8" t="s" s="12">
         <v>81</v>
       </c>
-      <c r="E8" t="s" s="10">
+      <c r="E8" t="s" s="12">
         <v>82</v>
       </c>
-      <c r="F8" t="s" s="10">
+      <c r="F8" t="s" s="12">
         <v>51</v>
       </c>
-      <c r="G8" t="s" s="10">
+      <c r="G8" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="H8" t="s" s="10">
+      <c r="H8" t="s" s="12">
         <v>28</v>
       </c>
-      <c r="I8" t="s" s="10">
+      <c r="I8" t="s" s="12">
         <v>83</v>
       </c>
-      <c r="J8" t="s" s="10">
+      <c r="J8" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K8" t="s" s="10">
+      <c r="K8" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L8" t="s" s="10">
+      <c r="L8" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="M8" t="s" s="10">
+      <c r="M8" t="s" s="12">
         <v>84</v>
       </c>
-      <c r="N8" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="O8" t="s" s="10">
+      <c r="N8" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="O8" t="s" s="12">
         <v>85</v>
       </c>
-      <c r="P8" t="s" s="10">
+      <c r="P8" t="s" s="12">
         <v>84</v>
       </c>
-      <c r="Q8" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="S8" t="s" s="10">
+      <c r="Q8" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="R8" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="S8" t="s" s="12">
         <v>86</v>
       </c>
-      <c r="T8" t="s" s="10">
+      <c r="T8" t="s" s="12">
         <v>87</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" t="s" s="8">
+      <c r="A9" t="s" s="10">
         <v>88</v>
       </c>
-      <c r="B9" t="s" s="9">
+      <c r="B9" t="s" s="11">
         <v>71</v>
       </c>
-      <c r="C9" t="s" s="10">
+      <c r="C9" t="s" s="12">
         <v>22</v>
       </c>
-      <c r="D9" t="s" s="10">
+      <c r="D9" t="s" s="12">
         <v>89</v>
       </c>
-      <c r="E9" t="s" s="10">
+      <c r="E9" t="s" s="12">
         <v>90</v>
       </c>
-      <c r="F9" t="s" s="10">
+      <c r="F9" t="s" s="12">
         <v>91</v>
       </c>
-      <c r="G9" t="s" s="10">
+      <c r="G9" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="H9" t="s" s="10">
+      <c r="H9" t="s" s="12">
         <v>92</v>
       </c>
-      <c r="I9" t="s" s="10">
+      <c r="I9" t="s" s="12">
         <v>93</v>
       </c>
-      <c r="J9" t="s" s="10">
+      <c r="J9" t="s" s="12">
         <v>56</v>
       </c>
-      <c r="K9" t="s" s="10">
+      <c r="K9" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L9" t="s" s="10">
+      <c r="L9" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="M9" t="s" s="10">
+      <c r="M9" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="N9" t="s" s="10">
+      <c r="N9" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="O9" t="s" s="10">
+      <c r="O9" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="P9" t="s" s="10">
+      <c r="P9" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="Q9" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="S9" t="s" s="10">
+      <c r="Q9" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="R9" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="S9" t="s" s="12">
         <v>94</v>
       </c>
-      <c r="T9" t="s" s="10">
+      <c r="T9" t="s" s="12">
         <v>95</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" t="s" s="8">
+      <c r="A10" t="s" s="10">
         <v>96</v>
       </c>
-      <c r="B10" t="s" s="9">
+      <c r="B10" t="s" s="11">
         <v>56</v>
       </c>
-      <c r="C10" t="s" s="10">
+      <c r="C10" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="D10" t="s" s="10">
+      <c r="D10" t="s" s="12">
         <v>61</v>
       </c>
-      <c r="E10" t="s" s="10">
+      <c r="E10" t="s" s="12">
         <v>97</v>
       </c>
-      <c r="F10" t="s" s="10">
+      <c r="F10" t="s" s="12">
         <v>98</v>
       </c>
-      <c r="G10" t="s" s="10">
+      <c r="G10" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="H10" t="s" s="10">
+      <c r="H10" t="s" s="12">
         <v>28</v>
       </c>
-      <c r="I10" t="s" s="10">
+      <c r="I10" t="s" s="12">
         <v>99</v>
       </c>
-      <c r="J10" t="s" s="10">
+      <c r="J10" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K10" t="s" s="10">
+      <c r="K10" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L10" t="s" s="10">
+      <c r="L10" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M10" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="N10" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="O10" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="P10" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="Q10" t="s" s="10">
+      <c r="M10" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="N10" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="O10" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="P10" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="s" s="12">
         <v>100</v>
       </c>
-      <c r="R10" t="s" s="10">
+      <c r="R10" t="s" s="12">
         <v>101</v>
       </c>
-      <c r="S10" t="s" s="10">
+      <c r="S10" t="s" s="12">
         <v>102</v>
       </c>
-      <c r="T10" t="s" s="10">
+      <c r="T10" t="s" s="12">
         <v>103</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" t="s" s="8">
+      <c r="A11" t="s" s="10">
         <v>104</v>
       </c>
-      <c r="B11" t="s" s="9">
+      <c r="B11" t="s" s="11">
         <v>56</v>
       </c>
-      <c r="C11" t="s" s="10">
+      <c r="C11" t="s" s="12">
         <v>22</v>
       </c>
-      <c r="D11" t="s" s="10">
+      <c r="D11" t="s" s="12">
         <v>105</v>
       </c>
-      <c r="E11" t="s" s="10">
+      <c r="E11" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="F11" t="s" s="10">
+      <c r="F11" t="s" s="12">
         <v>74</v>
       </c>
-      <c r="G11" t="s" s="10">
+      <c r="G11" t="s" s="12">
         <v>106</v>
       </c>
-      <c r="H11" t="s" s="10">
+      <c r="H11" t="s" s="12">
         <v>93</v>
       </c>
-      <c r="I11" t="s" s="10">
+      <c r="I11" t="s" s="12">
         <v>93</v>
       </c>
-      <c r="J11" t="s" s="10">
+      <c r="J11" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K11" t="s" s="10">
+      <c r="K11" t="s" s="12">
         <v>107</v>
       </c>
-      <c r="L11" t="s" s="10">
+      <c r="L11" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="M11" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="O11" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="P11" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="Q11" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="R11" t="s" s="10">
-        <v>34</v>
-      </c>
-      <c r="S11" t="s" s="10">
+      <c r="M11" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="N11" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="O11" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="P11" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="Q11" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="R11" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="S11" t="s" s="12">
         <v>108</v>
       </c>
-      <c r="T11" t="s" s="10">
+      <c r="T11" t="s" s="12">
         <v>109</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" t="s" s="8">
+      <c r="A12" t="s" s="10">
         <v>110</v>
       </c>
-      <c r="B12" t="s" s="9">
+      <c r="B12" t="s" s="11">
         <v>45</v>
       </c>
-      <c r="C12" t="s" s="10">
+      <c r="C12" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="D12" t="s" s="10">
+      <c r="D12" t="s" s="12">
         <v>111</v>
       </c>
-      <c r="E12" t="s" s="10">
+      <c r="E12" t="s" s="12">
         <v>112</v>
       </c>
-      <c r="F12" t="s" s="10">
+      <c r="F12" t="s" s="12">
         <v>113</v>
       </c>
-      <c r="G12" t="s" s="10">
+      <c r="G12" t="s" s="12">
         <v>114</v>
       </c>
-      <c r="H12" t="s" s="10">
+      <c r="H12" t="s" s="12">
         <v>115</v>
       </c>
-      <c r="I12" t="s" s="10">
+      <c r="I12" t="s" s="12">
         <v>116</v>
       </c>
-      <c r="J12" t="s" s="10">
+      <c r="J12" t="s" s="12">
         <v>117</v>
       </c>
-      <c r="K12" t="s" s="10">
+      <c r="K12" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="L12" t="s" s="10">
+      <c r="L12" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M12" t="s" s="10">
+      <c r="M12" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="N12" t="s" s="10">
+      <c r="N12" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="O12" t="s" s="10">
+      <c r="O12" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="P12" t="s" s="10">
+      <c r="P12" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="Q12" t="s" s="10">
+      <c r="Q12" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="R12" t="s" s="10">
+      <c r="R12" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="S12" t="s" s="10">
+      <c r="S12" t="s" s="12">
         <v>118</v>
       </c>
-      <c r="T12" t="s" s="10">
+      <c r="T12" t="s" s="12">
         <v>119</v>
       </c>
     </row>

--- a/docs/heros.xlsx
+++ b/docs/heros.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="113">
   <si>
     <t>Tableau 1</t>
   </si>
@@ -88,9 +88,6 @@
     <t>100-119</t>
   </si>
   <si>
-    <t>28-40</t>
-  </si>
-  <si>
     <t>3-6</t>
   </si>
   <si>
@@ -109,192 +106,177 @@
     <t>7</t>
   </si>
   <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>90</t>
   </si>
   <si>
+    <t>Aventurier solitaire</t>
+  </si>
+  <si>
+    <t>Discret comme une ombre et rapide comme un loup, la foret est son terrain de jeu.</t>
+  </si>
+  <si>
+    <t>KIARA</t>
+  </si>
+  <si>
+    <t>35-2100</t>
+  </si>
+  <si>
+    <t>101-122</t>
+  </si>
+  <si>
+    <t>3-5</t>
+  </si>
+  <si>
+    <t>99-90</t>
+  </si>
+  <si>
+    <t>101-95</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
+    <t>Nomade du désert</t>
+  </si>
+  <si>
+    <t>Des années de pérégrination dans le désert l’ont rendue insensible à la chaleur et à la soif.</t>
+  </si>
+  <si>
+    <t>MARKEN</t>
+  </si>
+  <si>
+    <t>37-2250</t>
+  </si>
+  <si>
+    <t>102-125</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>98-87</t>
+  </si>
+  <si>
+    <t>108-102</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Preux chevalier</t>
+  </si>
+  <si>
+    <t>Valeureux chevalier et gendre idéal. Que demander de plus ?</t>
+  </si>
+  <si>
+    <t>MIRA</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>24-1300</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>110-102</t>
+  </si>
+  <si>
+    <t>99-92</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Apprentie sorcière</t>
+  </si>
+  <si>
+    <t>En première année de magie à l’académie de Havrequignon.</t>
+  </si>
+  <si>
+    <t>CONSTELLO</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>32-2000</t>
+  </si>
+  <si>
+    <t>106-130</t>
+  </si>
+  <si>
+    <t>4-7</t>
+  </si>
+  <si>
+    <t>96-85</t>
+  </si>
+  <si>
+    <t>110-104</t>
+  </si>
+  <si>
+    <t>Saltimbanque survolté</t>
+  </si>
+  <si>
+    <t>Sa souplesse et son élégance n’ont d’égal que sa peur maladie de la magie .</t>
+  </si>
+  <si>
+    <t>SAHAD</t>
+  </si>
+  <si>
+    <t>27-1450</t>
+  </si>
+  <si>
+    <t>97-89</t>
+  </si>
+  <si>
+    <t>Aquamage</t>
+  </si>
+  <si>
+    <t>Sorcier adepte de la magie de l’eau. Disqualifié du concours régional d’apnée pour cause de triche.</t>
+  </si>
+  <si>
+    <t>SYRIO</t>
+  </si>
+  <si>
+    <t>46-2900</t>
+  </si>
+  <si>
+    <t>100-116</t>
+  </si>
+  <si>
+    <t>91-82</t>
+  </si>
+  <si>
+    <t>99-91</t>
+  </si>
+  <si>
     <t>95</t>
   </si>
   <si>
-    <t>Aventurier solitaire</t>
-  </si>
-  <si>
-    <t>Discret comme une ombre et rapide comme un loup, la foret est son terrain de jeu.</t>
-  </si>
-  <si>
-    <t>KIARA</t>
-  </si>
-  <si>
-    <t>35-2100</t>
-  </si>
-  <si>
-    <t>101-122</t>
-  </si>
-  <si>
-    <t>27-38</t>
-  </si>
-  <si>
-    <t>3-5</t>
-  </si>
-  <si>
-    <t>99-90</t>
-  </si>
-  <si>
-    <t>101-95</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Nomade du désert</t>
-  </si>
-  <si>
-    <t>Des années de pérégrination dans le désert l’ont rendue insensible à la chaleur et à la soif.</t>
-  </si>
-  <si>
-    <t>MARKEN</t>
-  </si>
-  <si>
-    <t>37-2250</t>
-  </si>
-  <si>
-    <t>102-125</t>
-  </si>
-  <si>
-    <t>25-35</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>98-87</t>
-  </si>
-  <si>
-    <t>108-102</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Preux chevalier</t>
-  </si>
-  <si>
-    <t>Valeureux chevalier et gendre idéal. Que demander de plus ?</t>
-  </si>
-  <si>
-    <t>MIRA</t>
-  </si>
-  <si>
-    <t>MAG</t>
-  </si>
-  <si>
-    <t>24-1300</t>
-  </si>
-  <si>
-    <t>12-19</t>
-  </si>
-  <si>
-    <t>2-5</t>
-  </si>
-  <si>
-    <t>110-102</t>
-  </si>
-  <si>
-    <t>99-92</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>Apprentie sorcière</t>
-  </si>
-  <si>
-    <t>En première année de magie à l’académie de Havrequignon.</t>
-  </si>
-  <si>
-    <t>CONSTELLO</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>32-2000</t>
-  </si>
-  <si>
-    <t>106-130</t>
-  </si>
-  <si>
-    <t>25-36</t>
-  </si>
-  <si>
-    <t>4-6</t>
-  </si>
-  <si>
-    <t>96-85</t>
-  </si>
-  <si>
-    <t>110-104</t>
-  </si>
-  <si>
-    <t>Saltimbanque survolté</t>
-  </si>
-  <si>
-    <t>Sa souplesse et son élégance n’ont d’égal que sa peur maladie de la magie .</t>
-  </si>
-  <si>
-    <t>SAHAD</t>
-  </si>
-  <si>
-    <t>27-1450</t>
-  </si>
-  <si>
-    <t>25-34</t>
-  </si>
-  <si>
-    <t>97-89</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Aquamage</t>
-  </si>
-  <si>
-    <t>Sorcier adepte de la magie de l’eau. Disqualifié du concours régional d’apnée pour cause de triche.</t>
-  </si>
-  <si>
-    <t>SYRIO</t>
-  </si>
-  <si>
-    <t>46-2900</t>
-  </si>
-  <si>
-    <t>100-116</t>
-  </si>
-  <si>
-    <t>12-16</t>
-  </si>
-  <si>
-    <t>91-82</t>
-  </si>
-  <si>
-    <t>99-91</t>
-  </si>
-  <si>
     <t>Défenseur inébranlable</t>
   </si>
   <si>
@@ -304,16 +286,13 @@
     <t>CERYS</t>
   </si>
   <si>
-    <t>12-18</t>
-  </si>
-  <si>
     <t>105-135</t>
   </si>
   <si>
     <t>100-92</t>
   </si>
   <si>
-    <t>115</t>
+    <t>120</t>
   </si>
   <si>
     <t>50</t>
@@ -337,6 +316,9 @@
     <t>1-3</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
     <t>Saurien mystérieux</t>
   </si>
   <si>
@@ -347,9 +329,6 @@
   </si>
   <si>
     <t>23-1200</t>
-  </si>
-  <si>
-    <t>35-42</t>
   </si>
   <si>
     <t>104-130</t>
@@ -1806,54 +1785,54 @@
         <v>24</v>
       </c>
       <c r="F3" t="s" s="9">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s" s="9">
         <v>25</v>
       </c>
-      <c r="G3" t="s" s="9">
+      <c r="H3" t="s" s="9">
         <v>26</v>
       </c>
-      <c r="H3" t="s" s="9">
+      <c r="I3" t="s" s="9">
         <v>27</v>
       </c>
-      <c r="I3" t="s" s="9">
+      <c r="J3" t="s" s="9">
         <v>28</v>
       </c>
-      <c r="J3" t="s" s="9">
+      <c r="K3" t="s" s="9">
         <v>29</v>
       </c>
-      <c r="K3" t="s" s="9">
+      <c r="L3" t="s" s="9">
         <v>30</v>
       </c>
-      <c r="L3" t="s" s="9">
+      <c r="M3" t="s" s="9">
         <v>31</v>
       </c>
-      <c r="M3" t="s" s="9">
+      <c r="N3" t="s" s="9">
         <v>32</v>
       </c>
-      <c r="N3" t="s" s="9">
+      <c r="O3" t="s" s="9">
         <v>33</v>
       </c>
-      <c r="O3" t="s" s="9">
+      <c r="P3" t="s" s="9">
         <v>34</v>
       </c>
-      <c r="P3" t="s" s="9">
-        <v>35</v>
-      </c>
       <c r="Q3" t="s" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R3" t="s" s="9">
         <v>34</v>
       </c>
       <c r="S3" t="s" s="9">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s" s="9">
         <v>36</v>
-      </c>
-      <c r="T3" t="s" s="9">
-        <v>37</v>
       </c>
     </row>
     <row r="4" ht="32.05" customHeight="1">
       <c r="A4" t="s" s="10">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s" s="11">
         <v>21</v>
@@ -1862,60 +1841,60 @@
         <v>22</v>
       </c>
       <c r="D4" t="s" s="12">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s" s="12">
         <v>39</v>
       </c>
-      <c r="E4" t="s" s="12">
+      <c r="F4" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="F4" t="s" s="12">
+      <c r="H4" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="G4" t="s" s="12">
+      <c r="I4" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="H4" t="s" s="12">
+      <c r="J4" t="s" s="12">
         <v>43</v>
       </c>
-      <c r="I4" t="s" s="12">
+      <c r="K4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="J4" t="s" s="12">
+      <c r="M4" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="O4" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="K4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s" s="12">
+      <c r="P4" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="S4" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="M4" t="s" s="12">
-        <v>33</v>
-      </c>
-      <c r="N4" t="s" s="12">
-        <v>33</v>
-      </c>
-      <c r="O4" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="P4" t="s" s="12">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="R4" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="S4" t="s" s="12">
+      <c r="T4" t="s" s="12">
         <v>47</v>
-      </c>
-      <c r="T4" t="s" s="12">
-        <v>48</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
       <c r="A5" t="s" s="10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s" s="11">
         <v>21</v>
@@ -1924,489 +1903,489 @@
         <v>22</v>
       </c>
       <c r="D5" t="s" s="12">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s" s="12">
         <v>50</v>
       </c>
-      <c r="E5" t="s" s="12">
+      <c r="F5" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s" s="12">
         <v>51</v>
       </c>
-      <c r="F5" t="s" s="12">
+      <c r="H5" t="s" s="12">
         <v>52</v>
       </c>
-      <c r="G5" t="s" s="12">
+      <c r="I5" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="H5" t="s" s="12">
+      <c r="J5" t="s" s="12">
         <v>54</v>
       </c>
-      <c r="I5" t="s" s="12">
+      <c r="K5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="12">
         <v>55</v>
       </c>
-      <c r="J5" t="s" s="12">
+      <c r="N5" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="O5" t="s" s="12">
+        <v>55</v>
+      </c>
+      <c r="P5" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="R5" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="S5" t="s" s="12">
         <v>56</v>
       </c>
-      <c r="K5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s" s="12">
-        <v>46</v>
-      </c>
-      <c r="M5" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="N5" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="P5" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="Q5" t="s" s="12">
-        <v>33</v>
-      </c>
-      <c r="R5" t="s" s="12">
-        <v>33</v>
-      </c>
-      <c r="S5" t="s" s="12">
+      <c r="T5" t="s" s="12">
         <v>57</v>
-      </c>
-      <c r="T5" t="s" s="12">
-        <v>58</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
       <c r="A6" t="s" s="10">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s" s="11">
         <v>21</v>
       </c>
       <c r="C6" t="s" s="12">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="D6" t="s" s="12">
+      <c r="E6" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s" s="12">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s" s="12">
         <v>61</v>
       </c>
-      <c r="E6" t="s" s="12">
+      <c r="H6" t="s" s="12">
         <v>62</v>
       </c>
-      <c r="F6" t="s" s="12">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s" s="12">
+      <c r="I6" t="s" s="12">
         <v>63</v>
       </c>
-      <c r="H6" t="s" s="12">
+      <c r="J6" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L6" t="s" s="12">
+        <v>30</v>
+      </c>
+      <c r="M6" t="s" s="12">
         <v>64</v>
       </c>
-      <c r="I6" t="s" s="12">
+      <c r="N6" t="s" s="12">
+        <v>64</v>
+      </c>
+      <c r="O6" t="s" s="12">
+        <v>64</v>
+      </c>
+      <c r="P6" t="s" s="12">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="R6" t="s" s="12">
         <v>65</v>
       </c>
-      <c r="J6" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M6" t="s" s="12">
+      <c r="S6" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="N6" t="s" s="12">
-        <v>66</v>
-      </c>
-      <c r="O6" t="s" s="12">
-        <v>66</v>
-      </c>
-      <c r="P6" t="s" s="12">
-        <v>66</v>
-      </c>
-      <c r="Q6" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s" s="12">
+      <c r="T6" t="s" s="12">
         <v>67</v>
-      </c>
-      <c r="S6" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="T6" t="s" s="12">
-        <v>69</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
       <c r="A7" t="s" s="10">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s" s="12">
         <v>22</v>
       </c>
       <c r="D7" t="s" s="12">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s" s="12">
+        <v>71</v>
+      </c>
+      <c r="F7" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s" s="12">
         <v>72</v>
       </c>
-      <c r="E7" t="s" s="12">
+      <c r="H7" t="s" s="12">
         <v>73</v>
       </c>
-      <c r="F7" t="s" s="12">
+      <c r="I7" t="s" s="12">
         <v>74</v>
       </c>
-      <c r="G7" t="s" s="12">
+      <c r="J7" t="s" s="12">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L7" t="s" s="12">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="N7" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="O7" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="P7" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="Q7" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="R7" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="S7" t="s" s="12">
         <v>75</v>
       </c>
-      <c r="H7" t="s" s="12">
+      <c r="T7" t="s" s="12">
         <v>76</v>
-      </c>
-      <c r="I7" t="s" s="12">
-        <v>77</v>
-      </c>
-      <c r="J7" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="K7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M7" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="N7" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="O7" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="P7" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="Q7" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="R7" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="S7" t="s" s="12">
-        <v>78</v>
-      </c>
-      <c r="T7" t="s" s="12">
-        <v>79</v>
       </c>
     </row>
     <row r="8" ht="32.05" customHeight="1">
       <c r="A8" t="s" s="10">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s" s="11">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s" s="12">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s" s="12">
+        <v>78</v>
+      </c>
+      <c r="E8" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s" s="12">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s" s="12">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s" s="12">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s" s="12">
+        <v>79</v>
+      </c>
+      <c r="J8" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="P8" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="R8" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="S8" t="s" s="12">
         <v>80</v>
       </c>
-      <c r="B8" t="s" s="11">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s" s="12">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s" s="12">
+      <c r="T8" t="s" s="12">
         <v>81</v>
-      </c>
-      <c r="E8" t="s" s="12">
-        <v>82</v>
-      </c>
-      <c r="F8" t="s" s="12">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s" s="12">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s" s="12">
-        <v>83</v>
-      </c>
-      <c r="J8" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="K8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L8" t="s" s="12">
-        <v>46</v>
-      </c>
-      <c r="M8" t="s" s="12">
-        <v>84</v>
-      </c>
-      <c r="N8" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="O8" t="s" s="12">
-        <v>85</v>
-      </c>
-      <c r="P8" t="s" s="12">
-        <v>84</v>
-      </c>
-      <c r="Q8" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="S8" t="s" s="12">
-        <v>86</v>
-      </c>
-      <c r="T8" t="s" s="12">
-        <v>87</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
       <c r="A9" t="s" s="10">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s" s="12">
         <v>22</v>
       </c>
       <c r="D9" t="s" s="12">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s" s="12">
+        <v>84</v>
+      </c>
+      <c r="F9" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s" s="12">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s" s="12">
+        <v>85</v>
+      </c>
+      <c r="I9" t="s" s="12">
+        <v>86</v>
+      </c>
+      <c r="J9" t="s" s="12">
+        <v>54</v>
+      </c>
+      <c r="K9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="M9" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="N9" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="O9" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="P9" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="R9" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="S9" t="s" s="12">
+        <v>88</v>
+      </c>
+      <c r="T9" t="s" s="12">
         <v>89</v>
-      </c>
-      <c r="E9" t="s" s="12">
-        <v>90</v>
-      </c>
-      <c r="F9" t="s" s="12">
-        <v>91</v>
-      </c>
-      <c r="G9" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="I9" t="s" s="12">
-        <v>93</v>
-      </c>
-      <c r="J9" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="K9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L9" t="s" s="12">
-        <v>46</v>
-      </c>
-      <c r="M9" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="N9" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="O9" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="P9" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="Q9" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="S9" t="s" s="12">
-        <v>94</v>
-      </c>
-      <c r="T9" t="s" s="12">
-        <v>95</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
       <c r="A10" t="s" s="10">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s" s="12">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s" s="12">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s" s="12">
+        <v>91</v>
+      </c>
+      <c r="G10" t="s" s="12">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s" s="12">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s" s="12">
+        <v>92</v>
+      </c>
+      <c r="J10" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="K10" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L10" t="s" s="12">
+        <v>30</v>
+      </c>
+      <c r="M10" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="N10" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="O10" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="P10" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="Q10" t="s" s="12">
+        <v>93</v>
+      </c>
+      <c r="R10" t="s" s="12">
+        <v>94</v>
+      </c>
+      <c r="S10" t="s" s="12">
+        <v>95</v>
+      </c>
+      <c r="T10" t="s" s="12">
         <v>96</v>
-      </c>
-      <c r="B10" t="s" s="11">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s" s="12">
-        <v>60</v>
-      </c>
-      <c r="D10" t="s" s="12">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s" s="12">
-        <v>97</v>
-      </c>
-      <c r="F10" t="s" s="12">
-        <v>98</v>
-      </c>
-      <c r="G10" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="H10" t="s" s="12">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s" s="12">
-        <v>99</v>
-      </c>
-      <c r="J10" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="K10" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M10" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="N10" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="O10" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="P10" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="Q10" t="s" s="12">
-        <v>100</v>
-      </c>
-      <c r="R10" t="s" s="12">
-        <v>101</v>
-      </c>
-      <c r="S10" t="s" s="12">
-        <v>102</v>
-      </c>
-      <c r="T10" t="s" s="12">
-        <v>103</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" t="s" s="10">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s" s="12">
         <v>22</v>
       </c>
       <c r="D11" t="s" s="12">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s" s="12">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="12">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s" s="12">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H11" t="s" s="12">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="12">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="K11" t="s" s="12">
+        <v>100</v>
+      </c>
+      <c r="L11" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="M11" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="N11" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="O11" t="s" s="12">
         <v>45</v>
-      </c>
-      <c r="K11" t="s" s="12">
-        <v>107</v>
-      </c>
-      <c r="L11" t="s" s="12">
-        <v>46</v>
-      </c>
-      <c r="M11" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="O11" t="s" s="12">
-        <v>34</v>
       </c>
       <c r="P11" t="s" s="12">
         <v>34</v>
       </c>
       <c r="Q11" t="s" s="12">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R11" t="s" s="12">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="S11" t="s" s="12">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="T11" t="s" s="12">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
       <c r="A12" t="s" s="10">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s" s="12">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s" s="12">
+        <v>105</v>
+      </c>
+      <c r="E12" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s" s="12">
+        <v>106</v>
+      </c>
+      <c r="G12" t="s" s="12">
+        <v>107</v>
+      </c>
+      <c r="H12" t="s" s="12">
+        <v>108</v>
+      </c>
+      <c r="I12" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="J12" t="s" s="12">
         <v>110</v>
       </c>
-      <c r="B12" t="s" s="11">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s" s="12">
-        <v>60</v>
-      </c>
-      <c r="D12" t="s" s="12">
+      <c r="K12" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L12" t="s" s="12">
+        <v>30</v>
+      </c>
+      <c r="M12" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="N12" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="O12" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="P12" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="R12" t="s" s="12">
+        <v>101</v>
+      </c>
+      <c r="S12" t="s" s="12">
         <v>111</v>
       </c>
-      <c r="E12" t="s" s="12">
+      <c r="T12" t="s" s="12">
         <v>112</v>
-      </c>
-      <c r="F12" t="s" s="12">
-        <v>113</v>
-      </c>
-      <c r="G12" t="s" s="12">
-        <v>114</v>
-      </c>
-      <c r="H12" t="s" s="12">
-        <v>115</v>
-      </c>
-      <c r="I12" t="s" s="12">
-        <v>116</v>
-      </c>
-      <c r="J12" t="s" s="12">
-        <v>117</v>
-      </c>
-      <c r="K12" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M12" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="N12" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="O12" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="P12" t="s" s="12">
-        <v>32</v>
-      </c>
-      <c r="Q12" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="R12" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="S12" t="s" s="12">
-        <v>118</v>
-      </c>
-      <c r="T12" t="s" s="12">
-        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/docs/heros.xlsx
+++ b/docs/heros.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="121">
   <si>
     <t>Tableau 1</t>
   </si>
@@ -88,6 +88,9 @@
     <t>100-119</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>3-6</t>
   </si>
   <si>
@@ -193,10 +196,10 @@
     <t>MAG</t>
   </si>
   <si>
-    <t>24-1300</t>
-  </si>
-  <si>
-    <t>2-5</t>
+    <t>25-1600</t>
+  </si>
+  <si>
+    <t>103-128</t>
   </si>
   <si>
     <t>110-102</t>
@@ -247,7 +250,7 @@
     <t>SAHAD</t>
   </si>
   <si>
-    <t>27-1450</t>
+    <t>29-1850</t>
   </si>
   <si>
     <t>97-89</t>
@@ -265,7 +268,7 @@
     <t>46-2900</t>
   </si>
   <si>
-    <t>100-116</t>
+    <t>100-112</t>
   </si>
   <si>
     <t>91-82</t>
@@ -283,6 +286,30 @@
     <t>Haut gradé de la garde royale. A une armure de plaques en guise de pyjama.</t>
   </si>
   <si>
+    <t>ZEVOR</t>
+  </si>
+  <si>
+    <t>32-2100</t>
+  </si>
+  <si>
+    <t>101-119</t>
+  </si>
+  <si>
+    <t>101-94</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>Mage de guerre</t>
+  </si>
+  <si>
+    <t>Spécialiste de l’enchantement d’arme et d’ustensile de cuisine.</t>
+  </si>
+  <si>
     <t>CERYS</t>
   </si>
   <si>
@@ -307,9 +334,6 @@
     <t>KEROS</t>
   </si>
   <si>
-    <t>32-2100</t>
-  </si>
-  <si>
     <t>3-4</t>
   </si>
   <si>
@@ -328,7 +352,7 @@
     <t>ORION</t>
   </si>
   <si>
-    <t>23-1200</t>
+    <t>24-1550</t>
   </si>
   <si>
     <t>104-130</t>
@@ -340,7 +364,7 @@
     <t>112-104</t>
   </si>
   <si>
-    <t>97-87</t>
+    <t>92-83</t>
   </si>
   <si>
     <t>6</t>
@@ -1658,7 +1682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="11.8516" style="1" customWidth="1"/>
@@ -1785,54 +1809,54 @@
         <v>24</v>
       </c>
       <c r="F3" t="s" s="9">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s" s="9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" t="s" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s" s="9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s" s="9">
+        <v>35</v>
+      </c>
+      <c r="Q3" t="s" s="9">
         <v>34</v>
       </c>
-      <c r="Q3" t="s" s="9">
-        <v>33</v>
-      </c>
       <c r="R3" t="s" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S3" t="s" s="9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="32.05" customHeight="1">
       <c r="A4" t="s" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="11">
         <v>21</v>
@@ -1841,60 +1865,60 @@
         <v>22</v>
       </c>
       <c r="D4" t="s" s="12">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s" s="12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s" s="12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s" s="12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s" s="12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M4" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s" s="12">
+        <v>35</v>
+      </c>
+      <c r="O4" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="P4" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="N4" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="O4" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="P4" t="s" s="12">
-        <v>31</v>
-      </c>
       <c r="Q4" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R4" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s" s="12">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T4" t="s" s="12">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
       <c r="A5" t="s" s="10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s" s="11">
         <v>21</v>
@@ -1903,489 +1927,551 @@
         <v>22</v>
       </c>
       <c r="D5" t="s" s="12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s" s="12">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s" s="12">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s" s="12">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I5" t="s" s="12">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J5" t="s" s="12">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K5" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M5" t="s" s="12">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5" t="s" s="12">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P5" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q5" t="s" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R5" t="s" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S5" t="s" s="12">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T5" t="s" s="12">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
       <c r="A6" t="s" s="10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s" s="11">
         <v>21</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s" s="12">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s" s="12">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s" s="12">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s" s="12">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s" s="12">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J6" t="s" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6" t="s" s="12">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N6" t="s" s="12">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O6" t="s" s="12">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P6" t="s" s="12">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q6" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s" s="12">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S6" t="s" s="12">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T6" t="s" s="12">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
       <c r="A7" t="s" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s" s="12">
         <v>22</v>
       </c>
       <c r="D7" t="s" s="12">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s" s="12">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s" s="12">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s" s="12">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s" s="12">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" t="s" s="12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7" t="s" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7" t="s" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N7" t="s" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="s" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R7" t="s" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s" s="12">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T7" t="s" s="12">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" ht="32.05" customHeight="1">
       <c r="A8" t="s" s="10">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s" s="12">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s" s="12">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s" s="12">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s" s="12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s" s="12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" t="s" s="12">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M8" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="N8" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="O8" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="N8" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="O8" t="s" s="12">
-        <v>31</v>
-      </c>
       <c r="P8" t="s" s="12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R8" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S8" t="s" s="12">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T8" t="s" s="12">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
       <c r="A9" t="s" s="10">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s" s="12">
         <v>22</v>
       </c>
       <c r="D9" t="s" s="12">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s" s="12">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s" s="12">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s" s="12">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s" s="12">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" t="s" s="12">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9" t="s" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M9" t="s" s="12">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N9" t="s" s="12">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O9" t="s" s="12">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P9" t="s" s="12">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="s" s="12">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R9" t="s" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S9" t="s" s="12">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T9" t="s" s="12">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
       <c r="A10" t="s" s="10">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s" s="12">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s" s="12">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s" s="12">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s" s="12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s" s="12">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="12">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L10" t="s" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M10" t="s" s="12">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="N10" t="s" s="12">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O10" t="s" s="12">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s" s="12">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="Q10" t="s" s="12">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="R10" t="s" s="12">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="S10" t="s" s="12">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T10" t="s" s="12">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" t="s" s="10">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s" s="12">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s" s="12">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s" s="12">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s" s="12">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="G11" t="s" s="12">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s" s="12">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s" s="12">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="J11" t="s" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s" s="12">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="L11" t="s" s="12">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M11" t="s" s="12">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="N11" t="s" s="12">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="O11" t="s" s="12">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="P11" t="s" s="12">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="s" s="12">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="R11" t="s" s="12">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="S11" t="s" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T11" t="s" s="12">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
       <c r="A12" t="s" s="10">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s" s="12">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s" s="12">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s" s="12">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s" s="12">
         <v>107</v>
       </c>
       <c r="H12" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s" s="12">
+        <v>87</v>
+      </c>
+      <c r="J12" t="s" s="12">
+        <v>44</v>
+      </c>
+      <c r="K12" t="s" s="12">
         <v>108</v>
       </c>
-      <c r="I12" t="s" s="12">
+      <c r="L12" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="M12" t="s" s="12">
         <v>109</v>
       </c>
-      <c r="J12" t="s" s="12">
+      <c r="N12" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="O12" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="P12" t="s" s="12">
+        <v>35</v>
+      </c>
+      <c r="Q12" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="R12" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="S12" t="s" s="12">
         <v>110</v>
       </c>
-      <c r="K12" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="L12" t="s" s="12">
+      <c r="T12" t="s" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" t="s" s="10">
+        <v>112</v>
+      </c>
+      <c r="B13" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s" s="12">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s" s="12">
+        <v>113</v>
+      </c>
+      <c r="E13" t="s" s="12">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s" s="12">
+        <v>114</v>
+      </c>
+      <c r="G13" t="s" s="12">
+        <v>115</v>
+      </c>
+      <c r="H13" t="s" s="12">
+        <v>116</v>
+      </c>
+      <c r="I13" t="s" s="12">
+        <v>117</v>
+      </c>
+      <c r="J13" t="s" s="12">
+        <v>118</v>
+      </c>
+      <c r="K13" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="M12" t="s" s="12">
-        <v>101</v>
-      </c>
-      <c r="N12" t="s" s="12">
-        <v>101</v>
-      </c>
-      <c r="O12" t="s" s="12">
-        <v>101</v>
-      </c>
-      <c r="P12" t="s" s="12">
+      <c r="L13" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="Q12" t="s" s="12">
-        <v>101</v>
-      </c>
-      <c r="R12" t="s" s="12">
-        <v>101</v>
-      </c>
-      <c r="S12" t="s" s="12">
-        <v>111</v>
-      </c>
-      <c r="T12" t="s" s="12">
-        <v>112</v>
+      <c r="M13" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="N13" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="O13" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="P13" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="Q13" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="R13" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="S13" t="s" s="12">
+        <v>119</v>
+      </c>
+      <c r="T13" t="s" s="12">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
